--- a/output/pdf_financials_xlsx/AURR.xlsx
+++ b/output/pdf_financials_xlsx/AURR.xlsx
@@ -2203,16 +2203,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.245933</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.8625</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.9977</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.0513</v>
       </c>
     </row>
     <row r="93">
@@ -3494,7 +3494,11 @@
           <t>Share-based payments reserve 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>1.245933</v>
       </c>

--- a/output/pdf_financials_xlsx/AURR.xlsx
+++ b/output/pdf_financials_xlsx/AURR.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001314</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.042291</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.139368</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.047911</v>
       </c>
     </row>
     <row r="13">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.279374</v>
+        <v>-1.280688</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.430685</v>
+        <v>-0.472976</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.212828</v>
+        <v>0.07346</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-14.396429</v>
+        <v>-14.44434</v>
       </c>
     </row>
     <row r="28">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.279374</v>
+        <v>-1.280688</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.430685</v>
+        <v>-0.472976</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.212828</v>
+        <v>0.07346</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-14.396429</v>
+        <v>-14.44434</v>
       </c>
     </row>
     <row r="30">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">

--- a/output/pdf_financials_xlsx/AURR.xlsx
+++ b/output/pdf_financials_xlsx/AURR.xlsx
@@ -2723,13 +2723,13 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0.366</v>
+        <v>7.110317</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0.0275</v>
+        <v>7.954322</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>-0.017067</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
@@ -4802,7 +4802,11 @@
           <t>Proceeds from issuance of common shares net of issuance costs</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -5172,7 +5176,11 @@
           <t>Proceeds from issuance of common shares net of issuance costs</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
         <v>7.110317</v>
       </c>

--- a/output/pdf_financials_xlsx/AURR.xlsx
+++ b/output/pdf_financials_xlsx/AURR.xlsx
@@ -4036,7 +4036,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>1.5875</v>
       </c>
@@ -4656,7 +4660,11 @@
           <t>Fair value of warrants issued in private placement $</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -5102,7 +5110,11 @@
           <t>Residual value of warrants associated with private placement $</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
